--- a/important_mails_2026-07-14.xlsx
+++ b/important_mails_2026-07-14.xlsx
@@ -2907,7 +2907,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2922,224 +2922,21 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Tue, 7 Jul 2026 14:45:21 +0000</t>
+          <t>Sat, 11 Jul 2026 04:26:29 +0000</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
+          <t>Create FBA removal order by 2026-07-23</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>96
- Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
- Dzień dobry Weihai EU,
- Niektóre z Twoich ofert zostały zdezaktywowane w naszych sklepach w Unii Europejskiej (UE) z powodu braku informacji o zgodności z wymogami. Działania te nie mają wpływu na kondycję Twojego konta.
- Przykłady zdezaktywowanych ofert znajdziesz na dole tej wiadomości e-mail. Aby wyświetlić ich pełną listę, przejdź na stronę „Kondycja konta”. Aby spełnić wymogi rozporządzenia w sprawie ogólnego bezpieczeństwa produktów, zapoznaj się z poniższymi ofertami i dalszymi działaniami do wykonania.
- Prześlij informacje dotyczące zgodności z wymogami
- Prześlij informacje dotyczące zgodności z wymogami
- Jak mogę ponownie aktywować oferty produktów?
- Aby ponownie aktywować oferty, dostarcz obowiązkowe informacje dotyczące zgodności z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów, postępując zgodnie z poniższymi instrukcjami:
--
- Przejdź na stronę Kondycja konta .
-- Wybierz „Dodaj filtry” i w kolumnie „Filtruj według podjętego działania” zaznacz pole „Usunięto ofertę”.
-- Obok zdezaktywowanej oferty produktu kliknij „Prześlij” i postępuj zg</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 7 Jul 2026 12:00:55 +0000</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>96
- Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
- Hej Weihai EU!
- Vissa av dina produktposter har inaktiverats i våra butiker inom Europeiska unionen (EU) på grund av att information om överensstämmelse saknas. Den här åtgärden påverkar inte din kontostatus.
- Du hittar exempel på de produktposter som har inaktiverats längst ner i detta e-postmeddelande, och hela listan finns på sidan Kontostatus. Granska de berörda produktposterna och nästa steg för att uppfylla kraven i Förordningen om allmän produktsäkerhet (GPSR) nedan.
- Skicka in information om överensstämmelse
- Skicka in information om överensstämmelse
- Hur återaktiverar jag mina produktposter?
- Om du vill återaktivera dina produktposter behöver du ange den efterfrågade GPSR-informationen om överensstämmelse genom att följa anvisningarna nedan:
--
- Gå till sidan Kontostatus .
-- Välj Lägg till filter och markera Produktpost borttagen i kolumnen Filtrera efter vidtagen åtgärd.
-- Klicka på Skicka in bredvid den inaktiverade produktposten och följ instruktionerna.
-- Följ stegen på Dolda produktposter för att åtgärda eventuella kvarstående problem med produktposter. Befintliga problem förhindrar att produktposter åter</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 7 Jul 2026 09:53:57 +0000</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>96
- Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate nei nostri negozi dell'Unione europea a causa della mancanza di informazioni relative alla conformità. Questa azione non avrà alcun impatto sullo stato del tuo account.
- Puoi trovare esempi delle tue offerte disattivate in fondo a questa e-mail e l'elenco completo nella pagina Stato dell'account. Rivedi le offerte interessate e i passaggi successivi per soddisfare i requisiti del Regolamento sulla sicurezza generale dei prodotti riportati di seguito.
- Inviare le informazioni sulla conformità
- Inviare le informazioni sulla conformità
- Come faccio a riattivare le mie offerte?
- Per riattivare le offerte, fornisci le informazioni richieste relative alla conformità al regolamento sulla sicurezza generale dei prodotti seguendo le istruzioni riportate di seguito:
--
- Vai alla pagina Stato dell'account .
-- Seleziona "Aggiungi filtri" e quindi "Offerta rimossa" nella colonna "Filtra per azione intrapresa".
-- Clicca su "Invia" accanto all'offerta disattivata e segui le istruzioni fornite.
-- Segui la procedura indi</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 7 Jul 2026 09:08:27 +0000</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>96
- Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
- Bonjour Weihai EU,
- Certaines de vos mises en vente ont été désactivées de nos boutiques en Union européenne (UE) en raison d’informations de conformité manquantes. Cette action n’affecte pas l’état de votre compte.
- Vous trouverez des exemples de vos mises en vente désactivées à la fin de cet e-mail, et la liste complète sur votre page État du compte. Passez en revue les mises en vente concernées et les étapes à suivre pour respecter les exigences du Règlement relatif à la sécurité générale des produits (RSGP) ci-dessous.
- Soumettre des informations de conformité
- Soumettre des informations de conformité
- Comment réactiver mes produits mis en vente ?
- Pour réactiver vos mises en vente, fournissez les informations de conformité pour la RSGP requises en suivant les instructions ci-dessous :
--
- Accédez à votre page État du compte .
-- Cliquez sur « Ajouter des filtres » et cochez « Mise en vente supprimée » dans la colonne « Filtrer par action prise ».
-- Cliquez sur « Soumettre » à côté du produit mis en vente désactivé et suivez les instructions fournies.
-- Suivez les étapes de la section Mise en vente supprimée</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 11 Jul 2026 04:26:29 +0000</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-07-23</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -3160,39 +2957,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 04:08:56 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -3215,39 +3012,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 03:06:39 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-23</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -3270,39 +3067,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 05:28:59 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0uWEj59btv)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3322,39 +3119,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 04:32:11 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3370,39 +3167,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 09:21:14 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3418,39 +3215,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 09:24:36 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3466,39 +3263,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 04:17:03 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (go0BbIMUoR)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3518,39 +3315,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 16:27:45 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (hbXn1jQJTV)</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3575,39 +3372,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 05:07:37 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3623,39 +3420,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 08:53:34 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (j2cKowrwuw)</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3675,39 +3472,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 04:56:23 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3723,39 +3520,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 23:44:37 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (H7OQM8penQ)</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3780,39 +3577,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 04:56:45 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3828,39 +3625,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 14:57:16 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3881,39 +3678,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 14:55:52 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $81.22 in an attempt to settle your Amazon seller account balance.
@@ -3929,39 +3726,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 04:47:15 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3977,39 +3774,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 04:59:26 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4025,39 +3822,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 03:07:14 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (HI24ImSBWG)</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4082,39 +3879,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 15:41:57 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4135,39 +3932,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 09:07:47 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Multchannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -4181,39 +3978,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 04:53:58 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4229,39 +4026,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 00:27:04 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FyqS0yVk5B)</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4286,39 +4083,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 04:45:26 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4334,39 +4131,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 15:11:41 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4387,39 +4184,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 02:24:45 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (1M28ecQsao)</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4444,39 +4241,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 06:20:20 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (9U/Ti42WHq)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4496,39 +4293,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 04:45:03 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4544,39 +4341,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 14:27:31 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4597,39 +4394,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 15:35:08 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (hCxOB8pPpU)</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4654,39 +4451,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 15:10:33 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4707,39 +4504,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 04:41:46 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4755,39 +4552,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 14:16:06 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4808,39 +4605,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:10:33 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Multchannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -4854,39 +4651,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 20:47:57 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (oWLDk2Qx2d)</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4911,39 +4708,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 20:39:11 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Emm3dPMsXA)</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4968,39 +4765,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 17:59:35 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai EU,
@@ -5014,39 +4811,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 15:48:24 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -5067,39 +4864,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 16:22:55 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -5120,39 +4917,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 15:05:28 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -5173,39 +4970,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 14:33:45 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $94.16 in an attempt to settle your Amazon seller account balance.
@@ -5221,39 +5018,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Seller News: June 2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5270,39 +5067,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:23:29 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5319,39 +5116,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 13:51:10 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5368,39 +5165,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 14:39:15 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5417,39 +5214,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 10:10:03 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -5473,39 +5270,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 17:09:13 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Access your January–March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -5521,39 +5318,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 16:54:53 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Access your January - March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -5569,39 +5366,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5621,39 +5418,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:43:29 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5670,39 +5467,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:42:06 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5722,39 +5519,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:21:30 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5774,39 +5571,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5823,39 +5620,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 03:31:27 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5875,39 +5672,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 03:28:55 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5927,39 +5724,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:38:10 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5976,39 +5773,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:37:54 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6028,39 +5825,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:52:57 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6077,39 +5874,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:51:45 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6129,39 +5926,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:45:52 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6181,39 +5978,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:12 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Updated China tax report link for October - December 2025</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  We’re resending your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -6231,39 +6028,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:05 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -6279,39 +6076,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:38 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6331,39 +6128,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:19 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6380,39 +6177,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 16:37:09 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;informacion-vendedor@amazon.mx&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Pago del saldo en tu cuenta de pagos de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Estimado vendedor:
  Hemos realizado un cargo en tu tarjeta de crédito (Visa) por valor de MXN 192.85 con el fin de saldar tu cuenta de vendedor de Amazon.
@@ -6424,39 +6221,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 14:05:42 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6476,39 +6273,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 12:44:57 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6525,39 +6322,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 12:50:33 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6577,39 +6374,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 13:23:55 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6626,39 +6423,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:11:15 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6678,39 +6475,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:09:47 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6727,39 +6524,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 17:21:56 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January–March 2026</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -6776,39 +6573,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 16:54:51 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -6825,39 +6622,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 08:40:50 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Envía el número de registro de España para la responsabilidad ampliada del productor con respecto a los RAEE a más tardar el 30 de septiembre</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Presenta el número de registro de la responsabilidad ampliada del productor a más tardar el 30 de septiembre o se te inscribirá automáticamente en RAP: Pago en mi nombre.
  96
@@ -6866,39 +6663,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 14:39:03 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6918,39 +6715,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:27:04 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6970,39 +6767,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:25:49 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7019,39 +6816,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:24:48 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7071,39 +6868,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 06:40:46 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Seller Central &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>重要信息：即刻重新验证您的所有 付款账户或存款方式</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  亲爱的卖家，
@@ -7137,39 +6934,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:24:03 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7189,39 +6986,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:23:28 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7238,39 +7035,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 13:35:44 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7290,39 +7087,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:08:36 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7341,40 +7138,40 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 13:22:39 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Get answers from the people who build the tools you use every day.
  Save $100</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49s9x/6752554013/h/2aeQsjjzcdEfNdbvcpArxhFF9Du4sBW3WI4zsTSQPBE)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4bmtj/6752554013/h/2aeQsjjzcdEfNdbvcpArxhFF9Du4sBW3WI4zsTSQPBE)
@@ -7391,39 +7188,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 13:08:44 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7442,40 +7239,40 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 08:00:54 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7490,40 +7287,40 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 05:35:29 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7548,40 +7345,40 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 06:41:28 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7596,39 +7393,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:09:44 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant is now live in France, Italy &amp; Spain</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  AI-powered assistance is now available in Seller Central to help you manage your business more efficiently.
@@ -7646,40 +7443,40 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 13:15:52 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>The Amazon Accelerate 2026 speaker lineup is here! Register now to
  save $100</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49sbm/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z49sbq/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
@@ -7696,40 +7493,40 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 04:09:19 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7741,40 +7538,40 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 04:08:32 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7786,40 +7583,40 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 02:52:15 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7838,39 +7635,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 12:40:58 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -7886,39 +7683,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:56:40 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7944,39 +7741,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:39:22 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -8002,39 +7799,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:15:17 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Submit EPR registration numbers by June 30</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -8043,39 +7840,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 04:34:37 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -8100,40 +7897,40 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 06:03:25 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -8151,40 +7948,40 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 19:23:07 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -8209,39 +8006,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:11:59 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -8260,39 +8057,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:32 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8311,39 +8108,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:28 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -8362,39 +8159,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:32:14 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>"pars-rp-core-sellerappeals-transfer@amazon.com" &lt;pars-rp-core-sellerappeals-transfer@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20516062511] 危险物品（危险品）</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20516062511] 危险物品（危险品）
@@ -8422,39 +8219,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:22 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8473,39 +8270,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 20:37:03 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Important message: your account is at risk of deactivation</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  96
@@ -8525,40 +8322,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 06:46:26 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -8571,6 +8368,209 @@
 Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
 → The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
 The SDS does not include the legislation/regulation in accordance with the document was created</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Jul 2026 14:45:21 +0000</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
+ Dzień dobry Weihai EU,
+ Niektóre z Twoich ofert zostały zdezaktywowane w naszych sklepach w Unii Europejskiej (UE) z powodu braku informacji o zgodności z wymogami. Działania te nie mają wpływu na kondycję Twojego konta.
+ Przykłady zdezaktywowanych ofert znajdziesz na dole tej wiadomości e-mail. Aby wyświetlić ich pełną listę, przejdź na stronę „Kondycja konta”. Aby spełnić wymogi rozporządzenia w sprawie ogólnego bezpieczeństwa produktów, zapoznaj się z poniższymi ofertami i dalszymi działaniami do wykonania.
+ Prześlij informacje dotyczące zgodności z wymogami
+ Prześlij informacje dotyczące zgodności z wymogami
+ Jak mogę ponownie aktywować oferty produktów?
+ Aby ponownie aktywować oferty, dostarcz obowiązkowe informacje dotyczące zgodności z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów, postępując zgodnie z poniższymi instrukcjami:
+-
+ Przejdź na stronę Kondycja konta .
+- Wybierz „Dodaj filtry” i w kolumnie „Filtruj według podjętego działania” zaznacz pole „Usunięto ofertę”.
+- Obok zdezaktywowanej oferty produktu kliknij „Prześlij” i postępuj zg</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Jul 2026 12:00:55 +0000</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
+ Hej Weihai EU!
+ Vissa av dina produktposter har inaktiverats i våra butiker inom Europeiska unionen (EU) på grund av att information om överensstämmelse saknas. Den här åtgärden påverkar inte din kontostatus.
+ Du hittar exempel på de produktposter som har inaktiverats längst ner i detta e-postmeddelande, och hela listan finns på sidan Kontostatus. Granska de berörda produktposterna och nästa steg för att uppfylla kraven i Förordningen om allmän produktsäkerhet (GPSR) nedan.
+ Skicka in information om överensstämmelse
+ Skicka in information om överensstämmelse
+ Hur återaktiverar jag mina produktposter?
+ Om du vill återaktivera dina produktposter behöver du ange den efterfrågade GPSR-informationen om överensstämmelse genom att följa anvisningarna nedan:
+-
+ Gå till sidan Kontostatus .
+- Välj Lägg till filter och markera Produktpost borttagen i kolumnen Filtrera efter vidtagen åtgärd.
+- Klicka på Skicka in bredvid den inaktiverade produktposten och följ instruktionerna.
+- Följ stegen på Dolda produktposter för att åtgärda eventuella kvarstående problem med produktposter. Befintliga problem förhindrar att produktposter åter</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Jul 2026 09:53:57 +0000</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate nei nostri negozi dell'Unione europea a causa della mancanza di informazioni relative alla conformità. Questa azione non avrà alcun impatto sullo stato del tuo account.
+ Puoi trovare esempi delle tue offerte disattivate in fondo a questa e-mail e l'elenco completo nella pagina Stato dell'account. Rivedi le offerte interessate e i passaggi successivi per soddisfare i requisiti del Regolamento sulla sicurezza generale dei prodotti riportati di seguito.
+ Inviare le informazioni sulla conformità
+ Inviare le informazioni sulla conformità
+ Come faccio a riattivare le mie offerte?
+ Per riattivare le offerte, fornisci le informazioni richieste relative alla conformità al regolamento sulla sicurezza generale dei prodotti seguendo le istruzioni riportate di seguito:
+-
+ Vai alla pagina Stato dell'account .
+- Seleziona "Aggiungi filtri" e quindi "Offerta rimossa" nella colonna "Filtra per azione intrapresa".
+- Clicca su "Invia" accanto all'offerta disattivata e segui le istruzioni fornite.
+- Segui la procedura indi</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Jul 2026 09:08:27 +0000</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente ont été désactivées de nos boutiques en Union européenne (UE) en raison d’informations de conformité manquantes. Cette action n’affecte pas l’état de votre compte.
+ Vous trouverez des exemples de vos mises en vente désactivées à la fin de cet e-mail, et la liste complète sur votre page État du compte. Passez en revue les mises en vente concernées et les étapes à suivre pour respecter les exigences du Règlement relatif à la sécurité générale des produits (RSGP) ci-dessous.
+ Soumettre des informations de conformité
+ Soumettre des informations de conformité
+ Comment réactiver mes produits mis en vente ?
+ Pour réactiver vos mises en vente, fournissez les informations de conformité pour la RSGP requises en suivant les instructions ci-dessous :
+-
+ Accédez à votre page État du compte .
+- Cliquez sur « Ajouter des filtres » et cochez « Mise en vente supprimée » dans la colonne « Filtrer par action prise ».
+- Cliquez sur « Soumettre » à côté du produit mis en vente désactivé et suivez les instructions fournies.
+- Suivez les étapes de la section Mise en vente supprimée</t>
         </is>
       </c>
     </row>

--- a/important_mails_2026-07-14.xlsx
+++ b/important_mails_2026-07-14.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,21 +500,74 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Tue, 14 Jul 2026 04:45:43 +0000</t>
+          <t>Tue, 14 Jul 2026 15:08:13 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>FBA reimbursement notification</t>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID 7O4Dvkqn6u
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on July 15, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-2163841117990994</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 04:45:43 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -530,39 +583,135 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 14:58:09 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement attempted
+Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
+On 07/14/26 14:58 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
+ 259.63.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon Store,
+Amazon Services
+Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 15:11:01 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Your Accelerate 2026 session catalog is now live</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1s7/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
+[Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1sb/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
+Approachable formats, actionable takeaways, and proven strategies
+The Amazon Accelerate 2026 [session catalog](https://go.amazonsellerservices.com/e/229492/e-5a3b486e4e26-session-catalog/7z4n1sf/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk) is live. This year's lineup spans 80+ sessions across 11 breakout topics, built for every experience level. Whether you're still finding your footing or ready to take the next step, you'll find content that meets you where you are.
+New for 2026: Expect more interactive sessions, expanded Q&amp;A opportunities, and sessions featuring fellow sellers sharing their real-world strategies.
+Join us in person at Amazon Accelerate 2026 from September 22 to 24 in Seattle. Save $100 with early-bird pricing until August 8!
+[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1sb/6767228964/h/eXAL3an</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Jul 2026 14:23:23 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $88.37 in an attempt to settle your Amazon seller account balance.
@@ -578,39 +727,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 09:58:04 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -626,39 +775,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 05:37:52 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -674,39 +823,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 05:20:26 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -722,39 +871,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 03:39:42 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -770,39 +919,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 06:09:58 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>【官方提示】请尽快通过您的欧洲站卖家资质KYC审核，以保证正常销售</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">账户注册
 															资质审查
@@ -835,39 +984,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 08:27:01 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -884,40 +1033,40 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 08:25:53 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Information needed for your Selling on Amazon
  payment account</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 [Action Required] Information needed for your Selling on Amazon payment account
@@ -932,39 +1081,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:11:12 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -981,39 +1130,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 14:21:36 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1033,39 +1182,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 04:03:58 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1082,39 +1231,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 10:36:54 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1131,39 +1280,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 10:30:59 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1183,39 +1332,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 23:31:39 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1235,39 +1384,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:07:00 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>完成账户验证以恢复付款</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  完成账户验证以恢复付款
@@ -1310,39 +1459,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:05:39 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Completa la verificación de la cuenta para restaurar los pagos</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Completa la verificación de la cuenta para restaurar los pagos
@@ -1359,39 +1508,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:04:08 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Accountverificatie voltooien om vergoedingen te herstellen</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Accountverificatie voltooien om vergoedingen te herstellen
@@ -1408,39 +1557,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:02:02 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Complete account verification to restore disbursements</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Complete account verification to restore disbursements
@@ -1458,39 +1607,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:00:06 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Ukończ weryfikację konta, aby przywrócić wypłaty środków</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Ukończ weryfikację konta, aby przywrócić wypłaty środków
@@ -1507,39 +1656,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:59:04 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Slutför kontoverifieringen så att utbetalningarna kan återställas</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Slutför kontoverifieringen så att utbetalningarna kan återställas
@@ -1556,39 +1705,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:57:07 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Completa la verifica dell'account per ripristinare i pagamenti</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Completa la verifica dell'account per ripristinare i pagamenti
@@ -1605,39 +1754,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:55:07 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Complete account verification to restore disbursements</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Complete account verification to restore disbursements
@@ -1655,39 +1804,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:53:42 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Terminez la vérification du compte pour restaurer les versements.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Terminez la vérification du compte pour restaurer les versements.
@@ -1704,39 +1853,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:44:42 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>完成账户验证以恢复付款</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  完成账户验证以恢复付款
@@ -1779,39 +1928,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 15:12:23 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 13.18. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -1825,39 +1974,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 14:31:14 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1874,39 +2023,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 14:31:07 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1926,39 +2075,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 13:15:46 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1975,39 +2124,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 12:15:55 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Get your Ireland VAT registration covered – €1,250 paid by Amazon</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activate placement in Ireland and Amazon covers your VAT registration and filing costs.
@@ -2028,40 +2177,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 15:01:39 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Manage VAT &amp; EPR Requirements Directly Within Your Pan-European FBA
  Inventory Portal</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Visit the Pan-EU Portal to Manage Listings,﻿ Compliance &amp;amp; Expansion in EU
                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
@@ -2069,39 +2218,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 17:38:33 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -2121,91 +2270,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 7 Jul 2026 16:17:59 +0000</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Reactivate your EU listings - GPSR compliance required</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Reactivate your EU listings - GPSR compliance required
- Hello Weihai EU,
- Some of your listings have been deactivated from our European Union (EU) stores due to missing compliance information. This action does not impact your account health.
- You can find examples of your deactivated listings at the bottom of this email, and the full list on your Account Health page. Review the affected listings and next steps to meet General Product Safety Regulation (GPSR) requirements below.
- Submit compliance information
- Submit compliance information
- How do I reactivate my listings?
- To reactivate your listings, provide the required GPSR compliance information by following the instructions below:
--
- Go to your Account Health page .
-- Select 'Add filters' and check 'Listing removed' in the "Filter by action taken" column.
-- Click 'Submit' next to the deactivated listing and follow the instructions provided.
-- Follow the steps on Suppressed listings to resolve any outstanding listing issues. Existing issues prevent listings from being reactivated, even if you’ve fulfilled all compliance requirements.
- Note: If you’ve recently submitted information on your Account Health page, and no longer </t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Jul 2026 17:10:46 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -2221,40 +2318,40 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 22:17:55 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Credit Note for
  6/2026</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Credit Note for 6/2026
  96
@@ -2276,39 +2373,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 15:24:05 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 6/2026</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 6/2026
  96
@@ -2330,39 +2427,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 14:31:47 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2377,40 +2474,40 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 23:30:27 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -2428,39 +2525,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 20:04:53 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -2479,39 +2576,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 15:47:06 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -2529,39 +2626,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 14:10:23 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -2579,39 +2676,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 12:46:14 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -2630,39 +2727,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 10:28:11 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -2681,39 +2778,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 09:08:55 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -2732,39 +2829,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Jul 2026 08:53:55 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>解决定价错误以重新启售停售商品</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  因错价而被禁止显示
@@ -2802,108 +2899,6 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 7 Jul 2026 20:45:55 +0000</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
- Reglamento relativo a la seguridad general de los productos</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>96
- Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
- Hola, Weihai EU:
- Algunos de los listings de nuestras tiendas de la UE se han desactivado debido a que falta información de cumplimiento normativo obligatoria. Esta medida no afecta al estado de tu cuenta.
- Encontrarás ejemplos de listings desactivados al final de este correo electrónico y la lista completa en la página "Estado de la cuenta". Revisa los listings afectados y siguientes pasos para cumplir los requisitos del Reglamento relativo a la seguridad general de los productos que se indican a continuación.
- Presentar información sobre cumplimiento normativo
- Presentar información sobre cumplimiento normativo
- ¿Cómo puedo reactivar mis listings?
- Para reactivar tus listings, proporciona la información obligatoria del Reglamento relativo a la seguridad general de los productos. Para ello, sigue las instrucciones que se indican a continuación:
--
- Ve a la página "Estado de la cuenta" .
-- Selecciona "Añadir filtros" y marca "Listing retirado" en la columna "Filtrar según las medidas tomadas".
-- Haz clic en "Enviar" junto al listing desactivado y sigue las</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 7 Jul 2026 18:16:40 +0000</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
- Hallo Weihai EU,
- Sommige van je productvermeldingen zijn gedeactiveerd in onze stores van de Europese Unie (EU) omdat er nalevingsinformatie ontbreekt. Deze actie heeft geen invloed op je accountstatus.
- Onderaan deze e-mail vind je voorbeelden van je gedeactiveerde productvermeldingen. De volledige lijst staat op je pagina Accountstatus. Bekijk hieronder de betroffen productvermeldingen en de stappen die je moet volgen om te voldoen aan de vereisten van de Verordening algemene productveiligheid (VAPV).
- Nalevingsinformatie indienen
- Nalevingsinformatie indienen
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je je productvermeldingen opnieuw wilt activeren, moet je de vereiste nalevingsinformatie met betrekking tot de VAPV verstrekken door de onderstaande instructies te volgen:
--
- Ga naar je pagina Accountstatus .
-- Selecteer ‘Filters toevoegen’ en vink ‘Verwijderde productvermelding’ aan in de kolom ‘Filteren op ondernomen actie’.
-- Klik op ‘Indienen’ naast de gedeactiveerde productvermelding en volg de instructies.
-- Volg de stappen op Onderdrukte productvermeldingen om openstaande problemen met de </t>
-        </is>
-      </c>
-    </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
@@ -4920,7 +4915,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>KYC审核类</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4935,122 +4930,21 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 15:05:28 +0000</t>
+          <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
+          <t>Seller News: June 2026</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID wk+evdT2Xv
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 15, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-299069385178831</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 14 Jun 2026 14:33:45 +0000</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Balance paid on your Amazon seller account</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon Services.
- We have charged your credit card for $94.16 in an attempt to settle your Amazon seller account balance.
- Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
- You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
- You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
- Thank you for selling on Amazon.
- Amazon Services
- Help us improve your experience on selling on Amazon through this brief survey:
- https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202606141349
- Was this email helpful?
- SPC-USAmazon-263885014606701</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Seller News: June 2026</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5067,39 +4961,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:23:29 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5116,39 +5010,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 13:51:10 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5165,39 +5059,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 14:39:15 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5214,39 +5108,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 10:10:03 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -5270,39 +5164,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 17:09:13 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Access your January–March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -5318,39 +5212,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 16:54:53 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Access your January - March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -5366,39 +5260,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5418,39 +5312,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:43:29 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5467,39 +5361,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:42:06 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5519,39 +5413,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:21:30 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5571,39 +5465,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5620,39 +5514,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 03:31:27 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5672,39 +5566,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 03:28:55 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5724,39 +5618,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:38:10 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5773,39 +5667,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:37:54 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5825,39 +5719,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:52:57 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5874,39 +5768,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:51:45 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5926,39 +5820,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:45:52 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5978,39 +5872,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:12 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Updated China tax report link for October - December 2025</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  We’re resending your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -6028,39 +5922,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:05 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -6076,39 +5970,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:38 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6128,39 +6022,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:19 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6177,39 +6071,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 16:37:09 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;informacion-vendedor@amazon.mx&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Pago del saldo en tu cuenta de pagos de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Estimado vendedor:
  Hemos realizado un cargo en tu tarjeta de crédito (Visa) por valor de MXN 192.85 con el fin de saldar tu cuenta de vendedor de Amazon.
@@ -6221,39 +6115,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 14:05:42 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6273,39 +6167,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 12:44:57 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6322,39 +6216,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 12:50:33 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6374,39 +6268,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 13:23:55 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6423,39 +6317,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:11:15 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6475,39 +6369,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:09:47 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6524,39 +6418,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 17:21:56 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January–March 2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -6573,39 +6467,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 16:54:51 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -6622,39 +6516,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 08:40:50 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Envía el número de registro de España para la responsabilidad ampliada del productor con respecto a los RAEE a más tardar el 30 de septiembre</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Presenta el número de registro de la responsabilidad ampliada del productor a más tardar el 30 de septiembre o se te inscribirá automáticamente en RAP: Pago en mi nombre.
  96
@@ -6663,39 +6557,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 14:39:03 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6715,39 +6609,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:27:04 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6767,39 +6661,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:25:49 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6816,39 +6710,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:24:48 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6868,39 +6762,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 06:40:46 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Seller Central &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>重要信息：即刻重新验证您的所有 付款账户或存款方式</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  亲爱的卖家，
@@ -6934,39 +6828,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:24:03 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6986,39 +6880,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:23:28 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7035,91 +6929,91 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 14 Jun 2026 13:35:44 +0000</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Jul 2026 16:17:59 +0000</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 06/14/26 13:35 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 514.26.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Reactivate your EU listings - GPSR compliance required</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Reactivate your EU listings - GPSR compliance required
+ Hello Weihai EU,
+ Some of your listings have been deactivated from our European Union (EU) stores due to missing compliance information. This action does not impact your account health.
+ You can find examples of your deactivated listings at the bottom of this email, and the full list on your Account Health page. Review the affected listings and next steps to meet General Product Safety Regulation (GPSR) requirements below.
+ Submit compliance information
+ Submit compliance information
+ How do I reactivate my listings?
+ To reactivate your listings, provide the required GPSR compliance information by following the instructions below:
+-
+ Go to your Account Health page .
+- Select 'Add filters' and check 'Listing removed' in the "Filter by action taken" column.
+- Click 'Submit' next to the deactivated listing and follow the instructions provided.
+- Follow the steps on Suppressed listings to resolve any outstanding listing issues. Existing issues prevent listings from being reactivated, even if you’ve fulfilled all compliance requirements.
+ Note: If you’ve recently submitted information on your Account Health page, and no longer </t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Jul 2026 05:08:36 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7138,40 +7032,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 13:22:39 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Get answers from the people who build the tools you use every day.
  Save $100</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49s9x/6752554013/h/2aeQsjjzcdEfNdbvcpArxhFF9Du4sBW3WI4zsTSQPBE)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4bmtj/6752554013/h/2aeQsjjzcdEfNdbvcpArxhFF9Du4sBW3WI4zsTSQPBE)
@@ -7188,39 +7082,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 13:08:44 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7239,40 +7133,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 08:00:54 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7287,40 +7181,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 05:35:29 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7345,40 +7239,40 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 06:41:28 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7393,39 +7287,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:09:44 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant is now live in France, Italy &amp; Spain</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  AI-powered assistance is now available in Seller Central to help you manage your business more efficiently.
@@ -7443,40 +7337,40 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 13:15:52 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>The Amazon Accelerate 2026 speaker lineup is here! Register now to
  save $100</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49sbm/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z49sbq/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
@@ -7493,40 +7387,40 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 04:09:19 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7538,40 +7432,40 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 04:08:32 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -7583,40 +7477,40 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 02:52:15 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7635,39 +7529,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 12:40:58 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -7683,39 +7577,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:56:40 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7741,39 +7635,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:39:22 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7799,39 +7693,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:15:17 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Submit EPR registration numbers by June 30</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -7840,39 +7734,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 04:34:37 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -7897,40 +7791,40 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 06:03:25 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7948,40 +7842,40 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 19:23:07 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -8006,39 +7900,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:11:59 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -8057,39 +7951,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:32 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8108,39 +8002,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:28 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -8159,39 +8053,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:32:14 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>"pars-rp-core-sellerappeals-transfer@amazon.com" &lt;pars-rp-core-sellerappeals-transfer@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20516062511] 危险物品（危险品）</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20516062511] 危险物品（危险品）
@@ -8219,39 +8113,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:22 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8270,39 +8164,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 20:37:03 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Important message: your account is at risk of deactivation</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  96
@@ -8322,40 +8216,40 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 06:46:26 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -8368,6 +8262,108 @@
 Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
 → The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
 The SDS does not include the legislation/regulation in accordance with the document was created</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Jul 2026 20:45:55 +0000</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
+ Reglamento relativo a la seguridad general de los productos</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
+ Hola, Weihai EU:
+ Algunos de los listings de nuestras tiendas de la UE se han desactivado debido a que falta información de cumplimiento normativo obligatoria. Esta medida no afecta al estado de tu cuenta.
+ Encontrarás ejemplos de listings desactivados al final de este correo electrónico y la lista completa en la página "Estado de la cuenta". Revisa los listings afectados y siguientes pasos para cumplir los requisitos del Reglamento relativo a la seguridad general de los productos que se indican a continuación.
+ Presentar información sobre cumplimiento normativo
+ Presentar información sobre cumplimiento normativo
+ ¿Cómo puedo reactivar mis listings?
+ Para reactivar tus listings, proporciona la información obligatoria del Reglamento relativo a la seguridad general de los productos. Para ello, sigue las instrucciones que se indican a continuación:
+-
+ Ve a la página "Estado de la cuenta" .
+- Selecciona "Añadir filtros" y marca "Listing retirado" en la columna "Filtrar según las medidas tomadas".
+- Haz clic en "Enviar" junto al listing desactivado y sigue las</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Jul 2026 18:16:40 +0000</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
+ Hallo Weihai EU,
+ Sommige van je productvermeldingen zijn gedeactiveerd in onze stores van de Europese Unie (EU) omdat er nalevingsinformatie ontbreekt. Deze actie heeft geen invloed op je accountstatus.
+ Onderaan deze e-mail vind je voorbeelden van je gedeactiveerde productvermeldingen. De volledige lijst staat op je pagina Accountstatus. Bekijk hieronder de betroffen productvermeldingen en de stappen die je moet volgen om te voldoen aan de vereisten van de Verordening algemene productveiligheid (VAPV).
+ Nalevingsinformatie indienen
+ Nalevingsinformatie indienen
+ Hoe activeer ik mijn productvermeldingen opnieuw?
+ Als je je productvermeldingen opnieuw wilt activeren, moet je de vereiste nalevingsinformatie met betrekking tot de VAPV verstrekken door de onderstaande instructies te volgen:
+-
+ Ga naar je pagina Accountstatus .
+- Selecteer ‘Filters toevoegen’ en vink ‘Verwijderde productvermelding’ aan in de kolom ‘Filteren op ondernomen actie’.
+- Klik op ‘Indienen’ naast de gedeactiveerde productvermelding en volg de instructies.
+- Volg de stappen op Onderdrukte productvermeldingen om openstaande problemen met de </t>
         </is>
       </c>
     </row>
@@ -12827,7 +12823,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -12842,68 +12838,21 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Sun, 14 Jun 2026 13:34:40 +0000</t>
+          <t>Sat, 4 Jul 2026 04:34:30 +0000</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>Pagamento elaborato con successo</t>
+          <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr"/>
       <c r="H240" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-This title will display on mobile devices
- Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
- Tentativo di pagamento
-Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
-In data 06/14/26 13:34 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
- 221,30.
- Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
- Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
- Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 4 Jul 2026 04:34:30 +0000</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F241" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12927,39 +12876,39 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:35:02 +0000</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12982,39 +12931,39 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:23:13 +0000</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13035,39 +12984,39 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:46:44 +0000</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -13091,39 +13040,39 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:45:39 +0000</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -13147,39 +13096,39 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 03:25:54 +0000</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-09</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13201,39 +13150,39 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 04:59:29 +0000</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -13257,39 +13206,39 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 03:24:34 +0000</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-02</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13311,40 +13260,40 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 03:21:27 +0000</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>[Amazon.co.uk] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.co.uk] One or More of Your Amazon Listings Have Been Search Suppressed
@@ -13361,39 +13310,39 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 00:16:50 +0000</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>View your US Q3-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q3-2026
@@ -13423,39 +13372,39 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 12:14:25 +0000</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Connect with an Amazon expert at Seller Café—Save $100 with early-bird pricing</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z46y96/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/4uHYwMZ-ld-EM/7z46y99/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
@@ -13471,39 +13420,39 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 03:04:08 +0000</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Action Required: Transparency Barcode Required for Your Products</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello from Amazon Seller Services,
